--- a/разрушения/!!разрушения_подписи_текст2.xlsx
+++ b/разрушения/!!разрушения_подписи_текст2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\liferay-ce-portal-7.2.1-ga2\PeterhoffParts\Peterhoff\разрушения\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Disk E\arhiv_site\Петергоф_выкладка\разрушения\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E23F9CA-8CEE-4867-90BD-90987E7B71C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160D985E-21BF-4A4B-B4E9-CDAB5A8CBCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="690" windowWidth="19440" windowHeight="15000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -722,7 +722,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1012,13 +1012,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1026,18 +1026,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1093,21 +1093,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="87" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>68</v>
       </c>
@@ -1139,23 +1139,23 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
@@ -1170,13 +1170,13 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1184,13 +1184,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>44</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>45</v>
       </c>
@@ -1217,13 +1217,13 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -1231,23 +1231,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>76</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>78</v>
       </c>
@@ -1271,13 +1271,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C3719C-97B0-4173-8D69-73A3C6945F72}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -1285,17 +1285,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="116" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -1311,13 +1311,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FF31A-BF01-4369-823C-CB0879574729}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -1325,17 +1325,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="116" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -1354,13 +1354,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1368,13 +1368,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>40</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -1401,13 +1401,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -1415,23 +1415,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="87" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>82</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>58</v>
       </c>
@@ -1458,13 +1458,13 @@
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -1472,22 +1472,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>87</v>
       </c>
@@ -1506,13 +1506,13 @@
     <tabColor rgb="FFCC99FF"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1520,13 +1520,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
@@ -1574,18 +1574,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>80</v>
       </c>
@@ -1604,13 +1604,13 @@
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>32</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1656,18 +1656,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="87" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>72</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>74</v>
       </c>
@@ -1702,13 +1702,13 @@
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1716,13 +1716,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
@@ -1749,13 +1749,13 @@
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1763,13 +1763,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>52</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>53</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
@@ -1804,13 +1804,13 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -1818,22 +1818,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>89</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>91</v>
       </c>
